--- a/simulations/correction_peat_market/all_dig_inv.xlsx
+++ b/simulations/correction_peat_market/all_dig_inv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B96BFF-15F8-4D96-A538-34EEF1CE0C74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325A116E-1894-4202-BD13-61E64F2B9841}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -4180,7 +4180,13 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="AK2" t="str">
+            <v>HC</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="3">
@@ -4250,6 +4256,62 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AL3">
+            <v>-479036.53667522129</v>
+          </cell>
+          <cell r="AM3">
+            <v>-5.0996868266494699</v>
+          </cell>
+          <cell r="AN3">
+            <v>-34562.503224742322</v>
+          </cell>
+          <cell r="AO3">
+            <v>0.88092441684732015</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AL4">
+            <v>-684134.54392147821</v>
+          </cell>
+          <cell r="AM4">
+            <v>-6.3517927378926764</v>
+          </cell>
+          <cell r="AN4">
+            <v>-165147.24454810651</v>
+          </cell>
+          <cell r="AO4">
+            <v>0.63665305931573202</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AL5">
+            <v>-683048.02951931697</v>
+          </cell>
+          <cell r="AM5">
+            <v>-6.3578543683243343</v>
+          </cell>
+          <cell r="AN5">
+            <v>-163891.8494255149</v>
+          </cell>
+          <cell r="AO5">
+            <v>0.63214948940507365</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4427,7 +4489,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4446,62 +4508,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="results"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="AL3">
-            <v>-479036.53667522129</v>
-          </cell>
-          <cell r="AM3">
-            <v>-5.0996868266494699</v>
-          </cell>
-          <cell r="AN3">
-            <v>-34562.503224742322</v>
-          </cell>
-          <cell r="AO3">
-            <v>0.88092441684732015</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AL4">
-            <v>-684134.54392147821</v>
-          </cell>
-          <cell r="AM4">
-            <v>-6.3517927378926764</v>
-          </cell>
-          <cell r="AN4">
-            <v>-165147.24454810651</v>
-          </cell>
-          <cell r="AO4">
-            <v>0.63665305931573202</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AL5">
-            <v>-683048.02951931697</v>
-          </cell>
-          <cell r="AM5">
-            <v>-6.3578543683243343</v>
-          </cell>
-          <cell r="AN5">
-            <v>-163891.8494255149</v>
-          </cell>
-          <cell r="AO5">
-            <v>0.63214948940507365</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5603,11 +5609,11 @@
         <v>62</v>
       </c>
       <c r="C5" s="4">
-        <f>[4]results!$AL$3-[4]results!$AN$3</f>
+        <f>[2]results!$AL$3-[2]results!$AN$3</f>
         <v>-444474.03345047898</v>
       </c>
       <c r="D5" s="4">
-        <f>[4]results!$AN$3</f>
+        <f>[2]results!$AN$3</f>
         <v>-34562.503224742322</v>
       </c>
       <c r="E5" s="4">
@@ -5618,11 +5624,11 @@
         <v>62</v>
       </c>
       <c r="H5" s="4">
-        <f>[4]results!$AM$3-[4]results!$AO$3</f>
+        <f>[2]results!$AM$3-[2]results!$AO$3</f>
         <v>-5.9806112434967904</v>
       </c>
       <c r="I5" s="4">
-        <f>[4]results!$AO$3</f>
+        <f>[2]results!$AO$3</f>
         <v>0.88092441684732015</v>
       </c>
       <c r="J5" s="4">
@@ -5675,11 +5681,11 @@
         <v>43</v>
       </c>
       <c r="C8" s="4">
-        <f>[4]results!$AL$4-[4]results!$AN$4</f>
+        <f>[2]results!$AL$4-[2]results!$AN$4</f>
         <v>-518987.2993733717</v>
       </c>
       <c r="D8" s="4">
-        <f>[4]results!$AN$4</f>
+        <f>[2]results!$AN$4</f>
         <v>-165147.24454810651</v>
       </c>
       <c r="E8" s="4">
@@ -5690,11 +5696,11 @@
         <v>43</v>
       </c>
       <c r="H8" s="4">
-        <f>[4]results!$AM$4-[4]results!$AO$4</f>
+        <f>[2]results!$AM$4-[2]results!$AO$4</f>
         <v>-6.9884457972084082</v>
       </c>
       <c r="I8" s="4">
-        <f>[4]results!$AO$4</f>
+        <f>[2]results!$AO$4</f>
         <v>0.63665305931573202</v>
       </c>
       <c r="J8" s="4">
@@ -5747,11 +5753,11 @@
         <v>44</v>
       </c>
       <c r="C11" s="4">
-        <f>[4]results!$AL$5-[4]results!$AN$5</f>
+        <f>[2]results!$AL$5-[2]results!$AN$5</f>
         <v>-519156.18009380205</v>
       </c>
       <c r="D11" s="4">
-        <f>[4]results!$AN$5</f>
+        <f>[2]results!$AN$5</f>
         <v>-163891.8494255149</v>
       </c>
       <c r="E11" s="4">
@@ -5762,11 +5768,11 @@
         <v>44</v>
       </c>
       <c r="H11" s="4">
-        <f>[4]results!$AM$5-[4]results!$AO$5</f>
+        <f>[2]results!$AM$5-[2]results!$AO$5</f>
         <v>-6.9900038577294081</v>
       </c>
       <c r="I11" s="4">
-        <f>[4]results!$AO$5</f>
+        <f>[2]results!$AO$5</f>
         <v>0.63214948940507365</v>
       </c>
       <c r="J11" s="4">
@@ -5988,15 +5994,15 @@
         <v>69</v>
       </c>
       <c r="C3">
-        <f>[2]LCIA_HC!$C$70</f>
+        <f>[3]LCIA_HC!$C$70</f>
         <v>34.264521044421535</v>
       </c>
       <c r="D3">
-        <f>[2]LCIA_HC!$AG$30</f>
+        <f>[3]LCIA_HC!$AG$30</f>
         <v>45.531422488575686</v>
       </c>
       <c r="E3">
-        <f>[2]LCIA_HC!$AH$30</f>
+        <f>[3]LCIA_HC!$AH$30</f>
         <v>1.5340506341983027E-4</v>
       </c>
     </row>
@@ -6008,15 +6014,15 @@
         <v>72</v>
       </c>
       <c r="C4" s="4">
-        <f>SUM([2]LCIA_HC!$C$76:$C$79)-SUM([2]LCIA_HC!$C$82:$C$84)</f>
+        <f>SUM([3]LCIA_HC!$C$76:$C$79)-SUM([3]LCIA_HC!$C$82:$C$84)</f>
         <v>12.757911731511776</v>
       </c>
       <c r="D4" s="4">
-        <f>[2]LCIA_HC!$AG$35-[2]LCIA_HC!$AG$41</f>
+        <f>[3]LCIA_HC!$AG$35-[3]LCIA_HC!$AG$41</f>
         <v>0.99093003960003401</v>
       </c>
       <c r="E4" s="4">
-        <f>[2]LCIA_HC!$AH$35-[2]LCIA_HC!$AH$41</f>
+        <f>[3]LCIA_HC!$AH$35-[3]LCIA_HC!$AH$41</f>
         <v>1.3628330318815769E-5</v>
       </c>
       <c r="F4" s="4"/>
@@ -6035,11 +6041,11 @@
         <v>2.2679999999999998</v>
       </c>
       <c r="D6">
-        <f>[3]Feuil1!$D$3*20*0.6</f>
+        <f>[4]Feuil1!$D$3*20*0.6</f>
         <v>1.8746774058338329</v>
       </c>
       <c r="E6">
-        <f>[3]Feuil1!$E$3*20*0.6</f>
+        <f>[4]Feuil1!$E$3*20*0.6</f>
         <v>1.7357321270915453E-5</v>
       </c>
     </row>
